--- a/planilhas/Auditoria de Site Institucional - V4.xlsx
+++ b/planilhas/Auditoria de Site Institucional - V4.xlsx
@@ -735,7 +735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1621,8 +1621,185 @@
       </c>
       <c r="H31" s="7" t="inlineStr"/>
     </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>1.6 Copy e mensagem</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr"/>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Teste da substituição na home</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Troque o nome da empresa pelo de um concorrente e releia a primeira dobra. Se o texto continua funcionando, ele é preenchimento — não comunica nada específico. É o problema mais comum em site institucional.</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>Copy que só funciona para este negócio</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>Reescreva a headline dizendo o que a empresa faz, para quem, e o que muda para o cliente — com um dado concreto (anos, volume, região, tipo de projeto).</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Importante</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr"/>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Páginas de serviço começam pelo problema, não pela descrição</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Abra cada página de serviço: ela abre falando do que a empresa faz, ou do problema que o cliente tem? Página que só descreve o serviço informa, mas não converte.</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Problema do cliente antes da descrição do serviço</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Reestruture: problema → consequência de não resolver → como a empresa resolve → prova → próximo passo.</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Importante</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr"/>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Jargão de setor e linguagem interna</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Marque os termos que só alguém de dentro entende (nomes de processo interno, sigla de norma, jargão técnico sem tradução). Cliente não compra o que não entende.</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Vocabulário do cliente, não da empresa</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>Traduza cada termo técnico no efeito prático. Onde a sigla for necessária, explique na primeira ocorrência.</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Importante</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr"/>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Consistência da promessa entre home, serviços e contato</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Leia as três em sequência. A promessa muda de página para página? Mensagem inconsistente faz o visitante recomeçar o entendimento a cada clique e enfraquece a marca.</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Mesma promessa central em todas as páginas</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Defina a mensagem central em uma frase e alinhe as páginas a ela; ajuste títulos e chamadas divergentes.</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>Importante</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr"/>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Clichê de mercado e linguagem com cara de texto gerado por IA</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Procure 'soluções sob medida', 'excelência', 'comprometidos com a qualidade', 'parceiro estratégico' e afins. São frases que toda empresa usa — por isso não diferenciam nenhuma.</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Sem frase-padrão de institucional</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>Troque cada frase genérica por um fato: número, prazo, caso, região atendida, forma de trabalho.</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Bom ter</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="A21:H21"/>
@@ -1630,8 +1807,9 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A32:H32"/>
   </mergeCells>
-  <conditionalFormatting sqref="G4:G31">
+  <conditionalFormatting sqref="G4:G37">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -1648,7 +1826,7 @@
       <formula>"Pendente"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F31">
+  <conditionalFormatting sqref="F4:F37">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
       <formula>"Crítico"</formula>
     </cfRule>
@@ -1659,16 +1837,16 @@
       <formula>"Bom ter"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:A31">
+  <conditionalFormatting sqref="A4:A37">
     <cfRule type="expression" priority="9" dxfId="0">
       <formula>A4="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="G4:G31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G4:G37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>_Listas!$A$1:$A$5</formula1>
     </dataValidation>
-    <dataValidation sqref="A4:A31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A4:A37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>_Listas!$B$1:$B$1</formula1>
     </dataValidation>
   </dataValidations>
